--- a/artfynd/A 24663-2023 artfynd.xlsx
+++ b/artfynd/A 24663-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24663-2023 artfynd.xlsx
+++ b/artfynd/A 24663-2023 artfynd.xlsx
@@ -2614,7 +2614,7 @@
         <v>98420262</v>
       </c>
       <c r="B19" t="n">
-        <v>5113</v>
+        <v>5166</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>337702.1981248409</v>
+        <v>337702</v>
       </c>
       <c r="R19" t="n">
-        <v>6578065.813663634</v>
+        <v>6578066</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2691,19 +2691,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 24663-2023 artfynd.xlsx
+++ b/artfynd/A 24663-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98423160</v>
+        <v>98419243</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338054.821607654</v>
+        <v>337822</v>
       </c>
       <c r="R2" t="n">
-        <v>6578001.142457186</v>
+        <v>6578079</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,19 +745,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,37 +774,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98420212</v>
+        <v>98420126</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337707.4939943727</v>
+        <v>337726</v>
       </c>
       <c r="R3" t="n">
-        <v>6578117.727894546</v>
+        <v>6578148</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,52 +873,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98422711</v>
+        <v>98422591</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Årjäng, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>337935.7006938318</v>
+        <v>337978</v>
       </c>
       <c r="R4" t="n">
-        <v>6578089.558716713</v>
+        <v>6578004</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,19 +942,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,37 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98418691</v>
+        <v>98422931</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1007,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>337932.1075685824</v>
+        <v>338050</v>
       </c>
       <c r="R5" t="n">
-        <v>6578137.25218902</v>
+        <v>6578087</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,19 +1040,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,52 +1069,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98418778</v>
+        <v>98420035</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Årjäng, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>337905.1790781024</v>
+        <v>337762</v>
       </c>
       <c r="R6" t="n">
-        <v>6578130.225121169</v>
+        <v>6578112</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1205,19 +1138,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,15 +1167,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98423094</v>
+        <v>98418691</v>
       </c>
       <c r="B7" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,36 +1178,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Årjäng, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338041.5001022192</v>
+        <v>337933</v>
       </c>
       <c r="R7" t="n">
-        <v>6578012.958016443</v>
+        <v>6578137</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,19 +1236,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,37 +1265,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98422931</v>
+        <v>98420183</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,10 +1301,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338049.773612507</v>
+        <v>337704</v>
       </c>
       <c r="R8" t="n">
-        <v>6578086.726642797</v>
+        <v>6578098</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,19 +1334,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,52 +1363,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98423832</v>
+        <v>98422849</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Årjäng, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338092.9450827591</v>
+        <v>338041</v>
       </c>
       <c r="R9" t="n">
-        <v>6578042.453517329</v>
+        <v>6578132</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1546,19 +1432,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,52 +1461,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98418937</v>
+        <v>98420262</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Årjäng, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>337894.681617751</v>
+        <v>337702</v>
       </c>
       <c r="R10" t="n">
-        <v>6578112.271684151</v>
+        <v>6578066</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1660,19 +1536,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,15 +1565,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98422279</v>
+        <v>98418778</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,10 +1602,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>337945.6520249132</v>
+        <v>337906</v>
       </c>
       <c r="R11" t="n">
-        <v>6578010.921227145</v>
+        <v>6578130</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1774,19 +1635,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,15 +1664,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>98421708</v>
+        <v>98418937</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,10 +1701,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>337837.841613814</v>
+        <v>337895</v>
       </c>
       <c r="R12" t="n">
-        <v>6578016.555440139</v>
+        <v>6578112</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1888,19 +1734,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,15 +1763,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>98420350</v>
+        <v>98419094</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,10 +1800,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>337747.7775538431</v>
+        <v>337845</v>
       </c>
       <c r="R13" t="n">
-        <v>6578006.096977564</v>
+        <v>6578127</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,19 +1833,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,15 +1862,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>98420335</v>
+        <v>98420212</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,10 +1899,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>337751.7575864804</v>
+        <v>337708</v>
       </c>
       <c r="R14" t="n">
-        <v>6578003.370586002</v>
+        <v>6578118</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2116,19 +1932,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,12 +1964,7 @@
         <v>98420314</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,10 +1998,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>337685.7672815819</v>
+        <v>337686</v>
       </c>
       <c r="R15" t="n">
-        <v>6578076.741191307</v>
+        <v>6578076</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2230,19 +2031,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2269,15 +2060,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>98423209</v>
+        <v>98420335</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2311,10 +2097,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>338055.3789214284</v>
+        <v>337752</v>
       </c>
       <c r="R16" t="n">
-        <v>6578026.167067772</v>
+        <v>6578003</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2344,19 +2130,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,15 +2159,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>98421276</v>
+        <v>98420350</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2425,10 +2196,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>337817.6881393217</v>
+        <v>337748</v>
       </c>
       <c r="R17" t="n">
-        <v>6578012.305935433</v>
+        <v>6578006</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2458,19 +2229,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,12 +2261,7 @@
         <v>98421239</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2539,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>337782.366097678</v>
+        <v>337782</v>
       </c>
       <c r="R18" t="n">
-        <v>6577964.742630314</v>
+        <v>6577965</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2572,19 +2328,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2611,57 +2357,47 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>98420262</v>
+        <v>98421276</v>
       </c>
       <c r="B19" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Årjäng, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>337702</v>
+        <v>337818</v>
       </c>
       <c r="R19" t="n">
-        <v>6578066</v>
+        <v>6578012</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2720,37 +2456,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>98419243</v>
+        <v>98421307</v>
       </c>
       <c r="B20" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2762,10 +2493,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>337822.0822776338</v>
+        <v>337837</v>
       </c>
       <c r="R20" t="n">
-        <v>6578079.083938817</v>
+        <v>6578017</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2795,19 +2526,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,51 +2555,47 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>98420035</v>
+        <v>98422279</v>
       </c>
       <c r="B21" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4660</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Årjäng, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>337761.5004071181</v>
+        <v>337946</v>
       </c>
       <c r="R21" t="n">
-        <v>6578111.325864248</v>
+        <v>6578010</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2908,19 +2625,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2947,15 +2654,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>98422726</v>
+        <v>98422711</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2989,10 +2691,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>337968.3610855634</v>
+        <v>337936</v>
       </c>
       <c r="R22" t="n">
-        <v>6578098.896919914</v>
+        <v>6578090</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3022,19 +2724,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,51 +2753,47 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>98422591</v>
+        <v>98422726</v>
       </c>
       <c r="B23" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Årjäng, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>337977.6149434679</v>
+        <v>337968</v>
       </c>
       <c r="R23" t="n">
-        <v>6578003.931397057</v>
+        <v>6578099</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3135,19 +2823,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3174,51 +2852,47 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>98420183</v>
+        <v>98423160</v>
       </c>
       <c r="B24" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Årjäng, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>337703.5748694004</v>
+        <v>338055</v>
       </c>
       <c r="R24" t="n">
-        <v>6578097.959545732</v>
+        <v>6578001</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3248,19 +2922,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3287,51 +2951,47 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>98422849</v>
+        <v>98423209</v>
       </c>
       <c r="B25" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Årjäng, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>338040.9368093043</v>
+        <v>338055</v>
       </c>
       <c r="R25" t="n">
-        <v>6578131.576948453</v>
+        <v>6578026</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3361,19 +3021,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3403,12 +3053,7 @@
         <v>98423309</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3442,10 +3087,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>338043.8788176057</v>
+        <v>338044</v>
       </c>
       <c r="R26" t="n">
-        <v>6577984.740657637</v>
+        <v>6577985</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3475,19 +3120,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3514,15 +3149,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>98419094</v>
+        <v>98423371</v>
       </c>
       <c r="B27" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3556,10 +3186,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>337845.1135897101</v>
+        <v>338044</v>
       </c>
       <c r="R27" t="n">
-        <v>6578126.66076718</v>
+        <v>6577960</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3589,19 +3219,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3628,15 +3248,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109616656</v>
+        <v>98423832</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3662,16 +3277,18 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Galteviken 1, N om, Vrm</t>
+          <t>Årjäng, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>337794.7474062305</v>
+        <v>338093</v>
       </c>
       <c r="R28" t="n">
-        <v>6577990.795103953</v>
+        <v>6578042</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3696,34 +3313,14 @@
           <t>Silbodal</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>S-Årj-0330</t>
-        </is>
-      </c>
       <c r="Y28" t="inlineStr">
         <is>
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>6 dellokaler. Rapporterade koordinater RT90: 6582209-1291891; 6582248-1291861; 6582251-1291857; 6582256-1291927; 6582260-1291947 resp. 6582260-1291947, noggrannhet 25 m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3738,7 +3335,7 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3746,23 +3343,14 @@
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>109616654</v>
       </c>
       <c r="B29" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,10 +3382,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>337696.8644132739</v>
+        <v>337697</v>
       </c>
       <c r="R29" t="n">
-        <v>6578096.71338963</v>
+        <v>6578097</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3832,19 +3420,9 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2022-02-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3880,15 +3458,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109616657</v>
+        <v>109616656</v>
       </c>
       <c r="B30" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3916,14 +3489,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Galteviken 1, ONO om, Vrm</t>
+          <t>Galteviken 1, N om, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>337908.4733337766</v>
+        <v>337795</v>
       </c>
       <c r="R30" t="n">
-        <v>6578123.438879437</v>
+        <v>6577991</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3950,7 +3523,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>S-Årj-0329</t>
+          <t>S-Årj-0330</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3958,24 +3531,14 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>5 dellokaler rapporterade RT90: 6582332-1292046; 6582341-1292079; 6582355-1292005; 6582370-1291956 resp. 6582373-1292016</t>
+          <t>6 dellokaler. Rapporterade koordinater RT90: 6582209-1291891; 6582248-1291861; 6582251-1291857; 6582256-1291927; 6582260-1291947 resp. 6582260-1291947, noggrannhet 25 m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4003,6 +3566,322 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>109616657</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Galteviken 1, ONO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>337908</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6578123</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>S-Årj-0329</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>5 dellokaler rapporterade RT90: 6582332-1292046; 6582341-1292079; 6582355-1292005; 6582370-1291956 resp. 6582373-1292016</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>109616658</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Galteviken 1, NO om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>337946</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6578011</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>S-Årj-0328</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>98423094</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Årjäng, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>338041</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6578012</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
